--- a/test-data/qa/TestData.xlsx
+++ b/test-data/qa/TestData.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t xml:space="preserve">TestCaseID</t>
+    <t xml:space="preserve">RestaurantID</t>
   </si>
   <si>
     <t xml:space="preserve">Postcode</t>
